--- a/chapters/08/core/AIHE-B05/edit/xlsx/AIHE-B05_workbook.xlsx
+++ b/chapters/08/core/AIHE-B05/edit/xlsx/AIHE-B05_workbook.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Ree92be3d45844ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Record" sheetId="2" r:id="R6d26910edd3e4b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthetic Example" sheetId="3" r:id="R34898bce64ff4f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R972b3a84b2634ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Record" sheetId="2" r:id="R3acdd8782ab04f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthetic Example" sheetId="3" r:id="Rc7bd43523aad4410"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,8 +37,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF303033"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B2436"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +70,16 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2436"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -68,7 +88,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -129,6 +149,18 @@
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -336,19 +368,23 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>Digital Resource Companion — Core Resource Workbooks</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
+      <x:c r="B1" s="29"/>
       <x:c r="C1" s="4"/>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="32" t="str">
         <x:v>Artificial Intelligence in Healthcare Management and Economics
 Evidence, Value, Governance, and Lifecycle Decision-Making</x:v>
       </x:c>
-      <x:c r="B2" s="10"/>
+      <x:c r="B2" s="32"/>
       <x:c r="C2" s="10"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
     </x:row>
     <x:row r="4" ht="45" customHeight="1">
       <x:c r="A4" s="21" t="str">
@@ -371,7 +407,7 @@
         <x:v>Resource edition</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>V1.0 · 16 September 2026</x:v>
+        <x:v>V1.0 | September 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
@@ -443,7 +479,7 @@
         <x:v>Persistent record</x:v>
       </x:c>
       <x:c r="B15" s="24" t="str">
-        <x:v>https://doi.org/10.5281/zenodo.21753927 — Concept DOI; not a version-specific DOI for these revised files.</x:v>
+        <x:v>https://doi.org/10.5281/zenodo.21753927 — Concept DOI; cite the version-specific DOI of the archived release used.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
@@ -456,8 +492,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A3:B3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
